--- a/final_year.xlsx
+++ b/final_year.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\CUB_LOG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUB_LOG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD68399-7F88-4C61-918A-55581577F3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD84E9A3-560F-483D-B849-F2C8F8F6DA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1AD0B9F6-39C5-4C17-B4EF-F27F56A14BAD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>Shri Gayathri S</t>
   </si>
@@ -120,13 +120,19 @@
   </si>
   <si>
     <t>problem statement no.</t>
+  </si>
+  <si>
+    <t>N.Anbukarasi</t>
+  </si>
+  <si>
+    <t>R.K.Monica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +170,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -173,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -231,12 +243,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -259,10 +303,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{2CDE4683-6CA2-4CE3-90ED-06AFF0B391DD}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{05A8FEC4-580A-4420-A96A-8D6D7B65337C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -594,8 +648,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E75CEF6-1869-47CA-AA06-F3D2A2D3EFFA}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
@@ -835,7 +895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -850,6 +910,40 @@
       </c>
       <c r="E15">
         <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9">
+        <v>126004022</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9">
+        <v>326150022</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/final_year.xlsx
+++ b/final_year.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUB_LOG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD84E9A3-560F-483D-B849-F2C8F8F6DA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975D57F5-E85B-40CA-A9E4-A124EFAEE4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1AD0B9F6-39C5-4C17-B4EF-F27F56A14BAD}"/>
   </bookViews>
@@ -303,10 +303,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -759,7 +759,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -770,10 +770,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -909,7 +909,7 @@
         <v>22</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">

--- a/final_year.xlsx
+++ b/final_year.xlsx
@@ -827,7 +827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -878,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
